--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -571,6 +571,86 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nut</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rivet Nut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>k3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plain Washer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>k5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>/media/images/4cc4abf1-3d85-44a2-be6b-f6f3b3180919.jpg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Suvi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
